--- a/Data/ID_Generators/UK_IDGenerator.xlsx
+++ b/Data/ID_Generators/UK_IDGenerator.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC9CAD0-4F90-401E-9188-A978915D6CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451119AC-5D65-43AF-A11A-A989E2820B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="441">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -1362,6 +1362,9 @@
   </si>
   <si>
     <t>AB911914A</t>
+  </si>
+  <si>
+    <t>AB911915A</t>
   </si>
 </sst>
 </file>
@@ -5090,7 +5093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817E4E34-4D65-4931-861C-871B7875EF5F}">
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -8871,6 +8874,24 @@
       </c>
       <c r="G210" s="29" t="s">
         <v>439</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>239</v>
+      </c>
+      <c r="B211">
+        <v>911915</v>
+      </c>
+      <c r="C211" t="s">
+        <v>240</v>
+      </c>
+      <c r="E211" t="str">
+        <f t="shared" ref="E211" si="9">A211&amp;B211&amp;C211</f>
+        <v>AB911915A</v>
+      </c>
+      <c r="G211" s="29" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ID_Generators/UK_IDGenerator.xlsx
+++ b/Data/ID_Generators/UK_IDGenerator.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451119AC-5D65-43AF-A11A-A989E2820B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A76ACE-C52F-4896-B5ED-BFFF48422C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="475">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -1365,6 +1365,108 @@
   </si>
   <si>
     <t>AB911915A</t>
+  </si>
+  <si>
+    <t>AB911916A</t>
+  </si>
+  <si>
+    <t>AB911917A</t>
+  </si>
+  <si>
+    <t>AB911918A</t>
+  </si>
+  <si>
+    <t>AB911919A</t>
+  </si>
+  <si>
+    <t>AB911920A</t>
+  </si>
+  <si>
+    <t>AB911921A</t>
+  </si>
+  <si>
+    <t>AB911922A</t>
+  </si>
+  <si>
+    <t>AB911923A</t>
+  </si>
+  <si>
+    <t>AB911924A</t>
+  </si>
+  <si>
+    <t>AB911925A</t>
+  </si>
+  <si>
+    <t>AB911926A</t>
+  </si>
+  <si>
+    <t>AB911927A</t>
+  </si>
+  <si>
+    <t>AB911928A</t>
+  </si>
+  <si>
+    <t>AB911929A</t>
+  </si>
+  <si>
+    <t>AB911930A</t>
+  </si>
+  <si>
+    <t>AB911931A</t>
+  </si>
+  <si>
+    <t>AB911932A</t>
+  </si>
+  <si>
+    <t>AB911933A</t>
+  </si>
+  <si>
+    <t>AB911934A</t>
+  </si>
+  <si>
+    <t>AB911935A</t>
+  </si>
+  <si>
+    <t>AB911936A</t>
+  </si>
+  <si>
+    <t>AB911937A</t>
+  </si>
+  <si>
+    <t>AB911938A</t>
+  </si>
+  <si>
+    <t>AB911939A</t>
+  </si>
+  <si>
+    <t>AB911940A</t>
+  </si>
+  <si>
+    <t>AB911941A</t>
+  </si>
+  <si>
+    <t>AB911942A</t>
+  </si>
+  <si>
+    <t>AB911943A</t>
+  </si>
+  <si>
+    <t>AB911944A</t>
+  </si>
+  <si>
+    <t>AB911945A</t>
+  </si>
+  <si>
+    <t>AB911946A</t>
+  </si>
+  <si>
+    <t>AB911947A</t>
+  </si>
+  <si>
+    <t>AB911948A</t>
+  </si>
+  <si>
+    <t>AB911949A</t>
   </si>
 </sst>
 </file>
@@ -5093,7 +5195,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817E4E34-4D65-4931-861C-871B7875EF5F}">
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -8887,11 +8989,623 @@
         <v>240</v>
       </c>
       <c r="E211" t="str">
-        <f t="shared" ref="E211" si="9">A211&amp;B211&amp;C211</f>
+        <f t="shared" ref="E211:E226" si="9">A211&amp;B211&amp;C211</f>
         <v>AB911915A</v>
       </c>
       <c r="G211" s="29" t="s">
         <v>440</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>239</v>
+      </c>
+      <c r="B212">
+        <v>911916</v>
+      </c>
+      <c r="C212" t="s">
+        <v>240</v>
+      </c>
+      <c r="E212" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911916A</v>
+      </c>
+      <c r="G212" s="29" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>239</v>
+      </c>
+      <c r="B213">
+        <v>911917</v>
+      </c>
+      <c r="C213" t="s">
+        <v>240</v>
+      </c>
+      <c r="E213" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911917A</v>
+      </c>
+      <c r="G213" s="29" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>239</v>
+      </c>
+      <c r="B214">
+        <v>911918</v>
+      </c>
+      <c r="C214" t="s">
+        <v>240</v>
+      </c>
+      <c r="E214" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911918A</v>
+      </c>
+      <c r="G214" s="29" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>239</v>
+      </c>
+      <c r="B215">
+        <v>911919</v>
+      </c>
+      <c r="C215" t="s">
+        <v>240</v>
+      </c>
+      <c r="E215" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911919A</v>
+      </c>
+      <c r="G215" s="29" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>239</v>
+      </c>
+      <c r="B216">
+        <v>911920</v>
+      </c>
+      <c r="C216" t="s">
+        <v>240</v>
+      </c>
+      <c r="E216" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911920A</v>
+      </c>
+      <c r="G216" s="29" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>239</v>
+      </c>
+      <c r="B217">
+        <v>911921</v>
+      </c>
+      <c r="C217" t="s">
+        <v>240</v>
+      </c>
+      <c r="E217" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911921A</v>
+      </c>
+      <c r="G217" s="29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>239</v>
+      </c>
+      <c r="B218">
+        <v>911922</v>
+      </c>
+      <c r="C218" t="s">
+        <v>240</v>
+      </c>
+      <c r="E218" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911922A</v>
+      </c>
+      <c r="G218" s="29" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>239</v>
+      </c>
+      <c r="B219">
+        <v>911923</v>
+      </c>
+      <c r="C219" t="s">
+        <v>240</v>
+      </c>
+      <c r="E219" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911923A</v>
+      </c>
+      <c r="G219" s="29" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>239</v>
+      </c>
+      <c r="B220">
+        <v>911924</v>
+      </c>
+      <c r="C220" t="s">
+        <v>240</v>
+      </c>
+      <c r="E220" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911924A</v>
+      </c>
+      <c r="G220" s="29" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>239</v>
+      </c>
+      <c r="B221">
+        <v>911925</v>
+      </c>
+      <c r="C221" t="s">
+        <v>240</v>
+      </c>
+      <c r="E221" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911925A</v>
+      </c>
+      <c r="G221" s="29" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>239</v>
+      </c>
+      <c r="B222">
+        <v>911926</v>
+      </c>
+      <c r="C222" t="s">
+        <v>240</v>
+      </c>
+      <c r="E222" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911926A</v>
+      </c>
+      <c r="G222" s="29" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>239</v>
+      </c>
+      <c r="B223">
+        <v>911927</v>
+      </c>
+      <c r="C223" t="s">
+        <v>240</v>
+      </c>
+      <c r="E223" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911927A</v>
+      </c>
+      <c r="G223" s="29" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>239</v>
+      </c>
+      <c r="B224">
+        <v>911928</v>
+      </c>
+      <c r="C224" t="s">
+        <v>240</v>
+      </c>
+      <c r="E224" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911928A</v>
+      </c>
+      <c r="G224" s="29" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>239</v>
+      </c>
+      <c r="B225">
+        <v>911929</v>
+      </c>
+      <c r="C225" t="s">
+        <v>240</v>
+      </c>
+      <c r="E225" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911929A</v>
+      </c>
+      <c r="G225" s="29" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>239</v>
+      </c>
+      <c r="B226">
+        <v>911930</v>
+      </c>
+      <c r="C226" t="s">
+        <v>240</v>
+      </c>
+      <c r="E226" t="str">
+        <f t="shared" si="9"/>
+        <v>AB911930A</v>
+      </c>
+      <c r="G226" s="29" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>239</v>
+      </c>
+      <c r="B227">
+        <v>911931</v>
+      </c>
+      <c r="C227" t="s">
+        <v>240</v>
+      </c>
+      <c r="E227" t="str">
+        <f t="shared" ref="E227:E245" si="10">A227&amp;B227&amp;C227</f>
+        <v>AB911931A</v>
+      </c>
+      <c r="G227" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>239</v>
+      </c>
+      <c r="B228">
+        <v>911932</v>
+      </c>
+      <c r="C228" t="s">
+        <v>240</v>
+      </c>
+      <c r="E228" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911932A</v>
+      </c>
+      <c r="G228" s="29" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>239</v>
+      </c>
+      <c r="B229">
+        <v>911933</v>
+      </c>
+      <c r="C229" t="s">
+        <v>240</v>
+      </c>
+      <c r="E229" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911933A</v>
+      </c>
+      <c r="G229" s="29" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>239</v>
+      </c>
+      <c r="B230">
+        <v>911934</v>
+      </c>
+      <c r="C230" t="s">
+        <v>240</v>
+      </c>
+      <c r="E230" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911934A</v>
+      </c>
+      <c r="G230" s="29" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>239</v>
+      </c>
+      <c r="B231">
+        <v>911935</v>
+      </c>
+      <c r="C231" t="s">
+        <v>240</v>
+      </c>
+      <c r="E231" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911935A</v>
+      </c>
+      <c r="G231" s="29" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232">
+        <v>911936</v>
+      </c>
+      <c r="C232" t="s">
+        <v>240</v>
+      </c>
+      <c r="E232" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911936A</v>
+      </c>
+      <c r="G232" s="29" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>239</v>
+      </c>
+      <c r="B233">
+        <v>911937</v>
+      </c>
+      <c r="C233" t="s">
+        <v>240</v>
+      </c>
+      <c r="E233" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911937A</v>
+      </c>
+      <c r="G233" s="29" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>239</v>
+      </c>
+      <c r="B234">
+        <v>911938</v>
+      </c>
+      <c r="C234" t="s">
+        <v>240</v>
+      </c>
+      <c r="E234" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911938A</v>
+      </c>
+      <c r="G234" s="29" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>239</v>
+      </c>
+      <c r="B235">
+        <v>911939</v>
+      </c>
+      <c r="C235" t="s">
+        <v>240</v>
+      </c>
+      <c r="E235" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911939A</v>
+      </c>
+      <c r="G235" s="29" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236">
+        <v>911940</v>
+      </c>
+      <c r="C236" t="s">
+        <v>240</v>
+      </c>
+      <c r="E236" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911940A</v>
+      </c>
+      <c r="G236" s="29" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>239</v>
+      </c>
+      <c r="B237">
+        <v>911941</v>
+      </c>
+      <c r="C237" t="s">
+        <v>240</v>
+      </c>
+      <c r="E237" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911941A</v>
+      </c>
+      <c r="G237" s="29" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>239</v>
+      </c>
+      <c r="B238">
+        <v>911942</v>
+      </c>
+      <c r="C238" t="s">
+        <v>240</v>
+      </c>
+      <c r="E238" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911942A</v>
+      </c>
+      <c r="G238" s="29" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+      <c r="B239">
+        <v>911943</v>
+      </c>
+      <c r="C239" t="s">
+        <v>240</v>
+      </c>
+      <c r="E239" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911943A</v>
+      </c>
+      <c r="G239" s="29" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>911944</v>
+      </c>
+      <c r="C240" t="s">
+        <v>240</v>
+      </c>
+      <c r="E240" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911944A</v>
+      </c>
+      <c r="G240" s="29" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>911945</v>
+      </c>
+      <c r="C241" t="s">
+        <v>240</v>
+      </c>
+      <c r="E241" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911945A</v>
+      </c>
+      <c r="G241" s="29" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>239</v>
+      </c>
+      <c r="B242">
+        <v>911946</v>
+      </c>
+      <c r="C242" t="s">
+        <v>240</v>
+      </c>
+      <c r="E242" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911946A</v>
+      </c>
+      <c r="G242" s="29" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>239</v>
+      </c>
+      <c r="B243">
+        <v>911947</v>
+      </c>
+      <c r="C243" t="s">
+        <v>240</v>
+      </c>
+      <c r="E243" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911947A</v>
+      </c>
+      <c r="G243" s="29" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>239</v>
+      </c>
+      <c r="B244">
+        <v>911948</v>
+      </c>
+      <c r="C244" t="s">
+        <v>240</v>
+      </c>
+      <c r="E244" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911948A</v>
+      </c>
+      <c r="G244" s="29" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>239</v>
+      </c>
+      <c r="B245">
+        <v>911949</v>
+      </c>
+      <c r="C245" t="s">
+        <v>240</v>
+      </c>
+      <c r="E245" t="str">
+        <f t="shared" si="10"/>
+        <v>AB911949A</v>
+      </c>
+      <c r="G245" s="29" t="s">
+        <v>474</v>
       </c>
     </row>
   </sheetData>
